--- a/results/Int Task Remove ACC -1.0/Rando_7_permute.xlsx
+++ b/results/Int Task Remove ACC -1.0/Rando_7_permute.xlsx
@@ -440,827 +440,827 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6476184103735003</v>
+        <v>0.6437642308773326</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6476184103735003</v>
+        <v>0.6575204166706142</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6458528736503364</v>
+        <v>0.650386029818129</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6541952073721076</v>
+        <v>0.6523424300417175</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6785596141517687</v>
+        <v>0.6605525212140735</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6686726085020511</v>
+        <v>0.6606997644108852</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6724095460961999</v>
+        <v>0.6696010696251102</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6710557376686783</v>
+        <v>0.6712193631514624</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.67120298086549</v>
+        <v>0.6644230829962134</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6726740311950306</v>
+        <v>0.6577440447429836</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6732330026874844</v>
+        <v>0.6530650270169555</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6560371289708293</v>
+        <v>0.6669534553596523</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6573759367509545</v>
+        <v>0.6676882897051346</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6604652806068472</v>
+        <v>0.6738519767695237</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6573759367509545</v>
+        <v>0.6728662763340312</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6444568265577777</v>
+        <v>0.662303057289841</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6798589465440088</v>
+        <v>0.6587133628925037</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6646875680950441</v>
+        <v>0.6524324339260958</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6413607718859446</v>
+        <v>0.6524324339260958</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6688117592443463</v>
+        <v>0.6454589092792425</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6380397075031659</v>
+        <v>0.6545946982975055</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6229310949209387</v>
+        <v>0.6580371494980309</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6303641130827752</v>
+        <v>0.6889811165534512</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6258187195447382</v>
+        <v>0.6885107673067996</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6193905473815186</v>
+        <v>0.6885121489453756</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.619889516284387</v>
+        <v>0.6596051119048296</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6170360378711082</v>
+        <v>0.6715193760993896</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6199931391775856</v>
+        <v>0.6698916084799449</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6324105171907419</v>
+        <v>0.6711145559966272</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.621471097700006</v>
+        <v>0.654035924181991</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6206626417561178</v>
+        <v>0.654035924181991</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6196919419680218</v>
+        <v>0.672675610210546</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6196919419680218</v>
+        <v>0.6723961244643191</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6123516909677155</v>
+        <v>0.6722638819149037</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5630613400157271</v>
+        <v>0.6702038587981165</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5576474879442166</v>
+        <v>0.6713368024304207</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5569562739023474</v>
+        <v>0.6637606859875005</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.566445170265243</v>
+        <v>0.650975199982315</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.579890487378929</v>
+        <v>0.6381188556558757</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.576668900973621</v>
+        <v>0.6163803516783356</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5697853802111459</v>
+        <v>0.6163803516783356</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5697853802111459</v>
+        <v>0.6089364777848307</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5409942034340429</v>
+        <v>0.6044660874837756</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5739147031608732</v>
+        <v>0.6022438205227805</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5566369180143564</v>
+        <v>0.6022752034561492</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5569314044079797</v>
+        <v>0.5917569863541479</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5572108901542067</v>
+        <v>0.5938756304219445</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5197584185212204</v>
+        <v>0.5910071513612694</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5065939687923373</v>
+        <v>0.5652208411099847</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5201306714289775</v>
+        <v>0.5589249114961804</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4848337533514604</v>
+        <v>0.547434612967507</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4873627440763233</v>
+        <v>0.5473323717128844</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4719024057880393</v>
+        <v>0.5402185120620995</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4605443498087812</v>
+        <v>0.5504544801407218</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4697809984430907</v>
+        <v>0.5633135877443132</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4681735606484069</v>
+        <v>0.5582419872857671</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4680999390500011</v>
+        <v>0.5577430183828986</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4916831279034147</v>
+        <v>0.5501641386628264</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4965407717596233</v>
+        <v>0.5271195914771059</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4962612860133964</v>
+        <v>0.5280166696667962</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4610527928047421</v>
+        <v>0.5433706217847296</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4687680599899574</v>
+        <v>0.5002861965621674</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4708280831067446</v>
+        <v>0.4894748747051189</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4660209677470291</v>
+        <v>0.4928000840036254</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4797593896157624</v>
+        <v>0.4876957189731346</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4816980259148026</v>
+        <v>0.4871367474806808</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4884165395559177</v>
+        <v>0.4902683300016106</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4890491326467774</v>
+        <v>0.4901933267646288</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4815630200882354</v>
+        <v>0.4937366375812009</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4768840023622072</v>
+        <v>0.495470791370996</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4750148427458448</v>
+        <v>0.5063748803895747</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4717646366843201</v>
+        <v>0.4890045254584672</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4565267422067689</v>
+        <v>0.4890045254584672</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4638233729034621</v>
+        <v>0.4739503889115215</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4427214095555703</v>
+        <v>0.4743034962561543</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4211532418767547</v>
+        <v>0.4814106450909986</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4103200111794298</v>
+        <v>0.4814106450909986</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4103200111794298</v>
+        <v>0.486733111639555</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4105953520099289</v>
+        <v>0.4878660552718591</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4077677299757148</v>
+        <v>0.4957435663012825</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4516726511354701</v>
+        <v>0.4957435663012825</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4841693825733532</v>
+        <v>0.4993754993636568</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4753638051747496</v>
+        <v>0.4995936008817223</v>
       </c>
     </row>
     <row r="85">
@@ -1270,57 +1270,57 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4866754775732426</v>
+        <v>0.5208439916880623</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4780619479367004</v>
+        <v>0.501769286885013</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4960268022093585</v>
+        <v>0.5188954865420508</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4949824808228566</v>
+        <v>0.5597848828212586</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4949416237963954</v>
+        <v>0.5349422317173689</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4954269736904435</v>
+        <v>0.5072648530094457</v>
       </c>
     </row>
   </sheetData>
